--- a/Official Whitelist.xlsx
+++ b/Official Whitelist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bigba\aa Personal Projects\Letterboxd-List-Scraping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F99AA6-A08B-4690-8646-0B0C30A0BEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D96FF7-7F70-47A3-A9AA-F1A7859973E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2080" yWindow="2080" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="1168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="1179">
   <si>
     <t>Title</t>
   </si>
@@ -3529,6 +3529,39 @@
   </si>
   <si>
     <t>https://letterboxd.com/film/bethlehem-kudumba-unit/</t>
+  </si>
+  <si>
+    <t>Touch of Evil</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/touch-of-evil/</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/celine-1992/</t>
+  </si>
+  <si>
+    <t>Chiikawa The Movie The Secret Of The Mermaid</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/chiikawa-the-movie-the-secret-of-the-mermaid/</t>
+  </si>
+  <si>
+    <t>Barefoot Gen</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/barefoot-gen/</t>
+  </si>
+  <si>
+    <t>Mughal-e-Azam</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/mughal-e-azam/</t>
+  </si>
+  <si>
+    <t>Bommarillu</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/bommarillu/</t>
   </si>
 </sst>
 </file>
@@ -3880,7 +3913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D584"/>
+  <dimension ref="A1:D590"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.36328125" bestFit="1" customWidth="1"/>
@@ -10416,6 +10449,90 @@
       </c>
       <c r="D584" t="s">
         <v>1167</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A585" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B585">
+        <v>1958</v>
+      </c>
+      <c r="C585">
+        <v>1480</v>
+      </c>
+      <c r="D585" s="2" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A586" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B586">
+        <v>1992</v>
+      </c>
+      <c r="C586">
+        <v>123348</v>
+      </c>
+      <c r="D586" s="2" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A587" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B587">
+        <v>2026</v>
+      </c>
+      <c r="C587">
+        <v>1586876</v>
+      </c>
+      <c r="D587" s="2" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A588" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B588">
+        <v>1983</v>
+      </c>
+      <c r="C588">
+        <v>14087</v>
+      </c>
+      <c r="D588" s="2" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A589" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B589">
+        <v>1960</v>
+      </c>
+      <c r="C589">
+        <v>44519</v>
+      </c>
+      <c r="D589" s="2" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A590" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B590">
+        <v>2006</v>
+      </c>
+      <c r="C590">
+        <v>31626</v>
+      </c>
+      <c r="D590" s="2" t="s">
+        <v>1178</v>
       </c>
     </row>
   </sheetData>
@@ -10458,6 +10575,12 @@
     <hyperlink ref="D580" r:id="rId36" xr:uid="{28B0537F-268D-45E0-A8C6-5C80DC289D3F}"/>
     <hyperlink ref="D582" r:id="rId37" xr:uid="{DA526506-8F63-4272-9038-4DC447CD9688}"/>
     <hyperlink ref="D583" r:id="rId38" xr:uid="{DB074FD6-73BB-4903-AB26-82303258FC31}"/>
+    <hyperlink ref="D585" r:id="rId39" xr:uid="{9B8CE55C-0FF4-4BE9-893F-EBC70E7619EC}"/>
+    <hyperlink ref="D586" r:id="rId40" xr:uid="{5CBA54C4-819A-4AE2-B7A0-8E8724B94BB7}"/>
+    <hyperlink ref="D587" r:id="rId41" xr:uid="{68EB9356-017F-4D26-A555-B3908E95FF6B}"/>
+    <hyperlink ref="D588" r:id="rId42" xr:uid="{361CF928-7A26-4D4B-B2B5-6692ED525A5B}"/>
+    <hyperlink ref="D589" r:id="rId43" xr:uid="{A2602418-163A-4D76-92E7-B23DB5111938}"/>
+    <hyperlink ref="D590" r:id="rId44" xr:uid="{E472D130-2EE7-4678-8ED5-11F011F9574F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Official Whitelist.xlsx
+++ b/Official Whitelist.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bigba\aa Personal Projects\Letterboxd-List-Scraping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D96FF7-7F70-47A3-A9AA-F1A7859973E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3299FA-C814-4774-84DF-6A991DFB6389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="1179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="1189">
   <si>
     <t>Title</t>
   </si>
@@ -3562,6 +3562,36 @@
   </si>
   <si>
     <t>https://letterboxd.com/film/bommarillu/</t>
+  </si>
+  <si>
+    <t>Iron Boy</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/iron-boy/</t>
+  </si>
+  <si>
+    <t>La Commune (Paris, 1871)</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/la-commune-paris-1871/</t>
+  </si>
+  <si>
+    <t>Twenty Four Eyes</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/twenty-four-eyes/</t>
+  </si>
+  <si>
+    <t>Possible Love</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/possible-love/</t>
+  </si>
+  <si>
+    <t>Baththa</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/baththa/</t>
   </si>
 </sst>
 </file>
@@ -3913,7 +3943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D590"/>
+  <dimension ref="A1:D595"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.36328125" bestFit="1" customWidth="1"/>
@@ -10533,6 +10563,76 @@
       </c>
       <c r="D590" s="2" t="s">
         <v>1178</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A591" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B591">
+        <v>2026</v>
+      </c>
+      <c r="C591">
+        <v>947493</v>
+      </c>
+      <c r="D591" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A592" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B592">
+        <v>2000</v>
+      </c>
+      <c r="C592">
+        <v>63195</v>
+      </c>
+      <c r="D592" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A593" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B593">
+        <v>1954</v>
+      </c>
+      <c r="C593">
+        <v>43339</v>
+      </c>
+      <c r="D593" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A594" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B594">
+        <v>2026</v>
+      </c>
+      <c r="C594">
+        <v>1483525</v>
+      </c>
+      <c r="D594" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A595" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B595">
+        <v>2026</v>
+      </c>
+      <c r="C595">
+        <v>1515692</v>
+      </c>
+      <c r="D595" t="s">
+        <v>1188</v>
       </c>
     </row>
   </sheetData>
